--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -47,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -438,7 +438,7 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,47 +501,47 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ITC Grand Chola</t>
+          <t>Mementos by ITC Hotels, Ekaaya Udaipur</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NO ACTION POINT</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>[DRY RUN PASSED]</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>20:07:50</t>
+          <t>05:06:18</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>20:07:51</t>
+          <t>05:06:20</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.01</v>
+        <v>2.33</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Site automation failed: TUNNEL_PROCESS_DIED</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -47,8 +47,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -438,7 +438,7 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,47 +501,47 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mementos by ITC Hotels, Ekaaya Udaipur</t>
+          <t>ITC Grand Chola</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>NO ACTION POINT</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>[DRY RUN PASSED]</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>05:06:18</t>
+          <t>20:25:54</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>05:06:20</t>
+          <t>20:25:55</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Site automation failed: TUNNEL_PROCESS_DIED</t>
-        </is>
-      </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -501,12 +501,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ITC Grand Chola</t>
+          <t>WH Bhubaneswar</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -519,29 +519,82 @@
           <t>NO ACTION POINT</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>logs\downloads\2026-10-15\WH_Bhubaneswar\17-02-35_action_points.csv</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>[DRY RUN PASSED]</t>
+          <t>No Action Point</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>20:25:54</t>
+          <t>17:01:45</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>20:25:55</t>
+          <t>17:02:40</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>54.41</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ITC Maurya</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION POINT</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>logs\downloads\2026-10-15\ITC_Maurya\17-03-28_action_points.csv</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>No Action Point</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>17:02:40</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>17:03:37</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/daily_report.xlsx
+++ b/reports/daily_report.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>WH Bhubaneswar</t>
+          <t>ITC Grand Chola</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -519,82 +519,29 @@
           <t>NO ACTION POINT</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>logs\downloads\2026-10-15\WH_Bhubaneswar\17-02-35_action_points.csv</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>No Action Point</t>
+          <t>[DRY RUN PASSED]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>17:01:45</t>
+          <t>18:36:37</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>17:02:40</t>
+          <t>18:36:38</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>54.41</v>
+        <v>1.01</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ITC Maurya</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION POINT</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>logs\downloads\2026-10-15\ITC_Maurya\17-03-28_action_points.csv</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>No Action Point</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>17:02:40</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>17:03:37</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
